--- a/artfynd/A 20292-2025 artfynd.xlsx
+++ b/artfynd/A 20292-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>95465549</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520777.015104769</v>
+        <v>520777</v>
       </c>
       <c r="R2" t="n">
-        <v>6471434.194632268</v>
+        <v>6471434</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2021-06-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-06-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95465453</v>
+        <v>95465550</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520895.7173435261</v>
+        <v>520911</v>
       </c>
       <c r="R3" t="n">
-        <v>6471536.544110588</v>
+        <v>6471520</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +862,107 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>Isabelle Norström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>95465453</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Linköpings kommun - projekt Ostlänken naturvärdesinventering 2021, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>520895</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6471537</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sjögestad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Hanna Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
           <t>Amanda Andersson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20292-2025 artfynd.xlsx
+++ b/artfynd/A 20292-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95465549</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95465550</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95465453</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>